--- a/data/Table_S1_codeml_results.xlsx
+++ b/data/Table_S1_codeml_results.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q95"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -563,8 +563,6 @@
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -643,16 +641,6 @@
           <t>gene function</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Angiosperm-353 loci ID</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>paralogs identification</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -720,16 +708,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -797,16 +775,6 @@
           <t>precatalytic spliceosome</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>#5858</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -871,16 +839,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -948,16 +906,6 @@
           <t>zinc ion binding</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1025,16 +973,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1102,16 +1040,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1179,16 +1107,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1256,16 +1174,6 @@
           <t>Peptidase C45</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1333,16 +1241,6 @@
           <t>isocitrate lyase activity ; oxo-acid-lyase activity ; carbon-carbon lyase activity</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1410,16 +1308,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1487,16 +1375,6 @@
           <t>calcium-dependent phospholipid binding ; phospholipid binding ; lipid binding</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1564,16 +1442,6 @@
           <t>Protein of unknown function DUF1635</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1641,16 +1509,6 @@
           <t>ion channel activity ; channel activity ; passive transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1715,16 +1573,6 @@
           <t>unfolded protein binding ; ATP hydrolysis activity ; ATP binding</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1792,16 +1640,6 @@
           <t>Vacuolar protein sorting-associated protein 62</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1869,16 +1707,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1943,16 +1771,6 @@
           <t>hydrolase activity, hydrolyzing O-glycosyl compounds ; hydrolase activity, acting on glycosyl bonds</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2020,16 +1838,6 @@
           <t>thiol-dependent deubiquitinase ; deubiquitinase activity ; ubiquitin-like protein-specific protease activity</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2094,16 +1902,6 @@
           <t>transmembrane transport</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2171,16 +1969,6 @@
           <t>6-phosphofructokinase activity ; phosphofructokinase activity ; carbohydrate kinase activity</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2248,16 +2036,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2322,16 +2100,6 @@
           <t>metal ion binding ; nucleic acid binding</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2399,16 +2167,6 @@
           <t>annonymous</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2476,16 +2234,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2550,16 +2298,6 @@
           <t>acylphosphatase activity</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2627,16 +2365,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2704,16 +2432,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2781,16 +2499,6 @@
           <t>no function</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2858,16 +2566,6 @@
           <t>positive regulation of transcription, DNA-templated</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2935,16 +2633,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3012,16 +2700,6 @@
           <t>peptidyl-prolyl cis-trans isomerase activity</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3089,16 +2767,6 @@
           <t>DNA binding ; ATP binding</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3166,16 +2834,6 @@
           <t>transcription preinitiation complex assembly</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3240,16 +2898,6 @@
           <t>DNA binding ; nucleic acid binding ; heterocyclic compound binding</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3317,16 +2965,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3394,16 +3032,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3471,16 +3099,6 @@
           <t>Protein of unknown function</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3548,16 +3166,6 @@
           <t>structural constituent of ribosome ; RNA binding</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3625,16 +3233,6 @@
           <t>regulation of proton transport ; regulation of cation transmembrane transport ; regulation of ion transmembrane transport</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3702,16 +3300,6 @@
           <t>transmembrane transporter activity ; transporter activity</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3779,16 +3367,6 @@
           <t>Protein of unknown function UPF0301 ; Thioredoxin-like superfamily</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3856,16 +3434,6 @@
           <t>integral component of membrane</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3930,16 +3498,6 @@
           <t>calcium ion binding</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4004,16 +3562,6 @@
           <t>sequence-specific DNA binding</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4081,16 +3629,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4155,16 +3693,6 @@
           <t>protein folding</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4229,16 +3757,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4303,16 +3821,6 @@
           <t>DNA binding</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4380,16 +3888,6 @@
           <t>transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4457,16 +3955,6 @@
           <t>ATP binding ; nucleic acid binding ; protein binding</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4534,16 +4022,6 @@
           <t>protein serine/threonine phosphatase activity ; phosphoprotein phosphatase activity ; phosphatase activity</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4608,16 +4086,6 @@
           <t>thiol-dependent deubiquitinase</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4685,16 +4153,6 @@
           <t>translation initiation factor activity ; translation factor activity, RNA binding ; translation regulator activity, nucleic acid binding</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4759,16 +4217,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4836,16 +4284,6 @@
           <t>transferase activity</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4910,16 +4348,6 @@
           <t>No functional information found for HOM05D006296</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4984,16 +4412,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>#6641</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5058,16 +4476,6 @@
           <t>GTPase activity ; GTP binding ; guanyl ribonucleotide binding</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5135,16 +4543,6 @@
           <t>ubiquitin conjugating enzyme activity</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5209,16 +4607,6 @@
           <t>clathrin binding</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5283,16 +4671,6 @@
           <t>process utilizing autophagic mechanism ; autophagy ; cellular catabolic process</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5360,16 +4738,6 @@
           <t>Protein of unknown function DUF616</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5437,16 +4805,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5514,16 +4872,6 @@
           <t>Uncharacterized protein At1g76660-like</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5588,16 +4936,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5665,16 +5003,6 @@
           <t>protein transport ; establishment of protein localization ; protein localization</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5742,16 +5070,6 @@
           <t>Domain of unknown function DUF1308</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5819,16 +5137,6 @@
           <t>myosin heavy chain binding ; myosin XI tail binding ; myosin tail binding</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5893,16 +5201,6 @@
           <t>protein-disulfide reductase activity</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5970,16 +5268,6 @@
           <t>peroxidase activity ; oxidoreductase activity, acting on peroxide as acceptor ; antioxidant activity</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6047,16 +5335,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6124,16 +5402,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6201,16 +5469,6 @@
           <t>ATP binding ; adenyl ribonucleotide binding ; adenyl nucleotide binding</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6275,16 +5533,6 @@
           <t>alpha-amylase activity ; amylase activity ; calcium ion binding</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6352,16 +5600,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6429,16 +5667,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6503,16 +5731,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6577,16 +5795,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6651,16 +5859,6 @@
           <t>Mitochondrial glycoprotein ; Mitochondrial glycoprotein superfamily</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6725,16 +5923,6 @@
           <t>Trichome birefringence-like family ; PMR5 N-terminal domain ; PC-Esterase</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6802,16 +5990,6 @@
           <t>protein heterodimerization activity ; protein dimerization activity ; protein binding</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6879,16 +6057,6 @@
           <t>ATP hydrolysis activity ; ATP binding ; protein binding</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6953,16 +6121,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7027,16 +6185,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7101,16 +6249,6 @@
           <t>dolichol kinase activity</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7178,16 +6316,6 @@
           <t>No functional information found for ORTHO05D007246</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7255,16 +6383,6 @@
           <t>Clp, repeat (R) domain ; Clp, N-terminal domain superfamily ; P-loop containing nucleoside triphosphate hydrolase</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7329,16 +6447,6 @@
           <t>lipid metabolic process</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7406,16 +6514,6 @@
           <t>acyltransferase activity, transferring groups other than amino-acyl groups ; acyltransferase activity ; transferase activity</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7483,16 +6581,6 @@
           <t>Myb domain ; SANT/Myb domain ; Homeobox-like domain superfamily</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7557,16 +6645,6 @@
           <t>structural constituent of ribosome ; structural molecule activity</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7634,16 +6712,6 @@
           <t>ABC-type transporter activity ; ATPase-coupled transmembrane transporter activity ; primary active transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7711,16 +6779,6 @@
           <t>ACT domain-containing protein ACR1-12</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7786,16 +6844,6 @@
       <c r="O95" t="inlineStr">
         <is>
           <t>protein binding</t>
-        </is>
-      </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -7810,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7829,8 +6877,6 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7914,16 +6960,6 @@
           <t>gene function</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Angiosperm-353 loci ID</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>paralogs identification</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7996,16 +7032,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8073,16 +7099,6 @@
           <t>precatalytic spliceosome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>#5858</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -8147,16 +7163,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -8229,16 +7235,6 @@
           <t>zinc ion binding</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8311,16 +7307,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8393,16 +7379,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8470,16 +7446,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8547,16 +7513,6 @@
           <t>Peptidase C45</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8624,16 +7580,6 @@
           <t>isocitrate lyase activity ; oxo-acid-lyase activity ; carbon-carbon lyase activity</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8701,16 +7647,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8778,16 +7714,6 @@
           <t>calcium-dependent phospholipid binding ; phospholipid binding ; lipid binding</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8855,16 +7781,6 @@
           <t>Protein of unknown function DUF1635</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8937,16 +7853,6 @@
           <t>ion channel activity ; channel activity ; passive transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9011,16 +7917,6 @@
           <t>unfolded protein binding ; ATP hydrolysis activity ; ATP binding</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9093,16 +7989,6 @@
           <t>Vacuolar protein sorting-associated protein 62</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9170,16 +8056,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9244,16 +8120,6 @@
           <t>hydrolase activity, hydrolyzing O-glycosyl compounds ; hydrolase activity, acting on glycosyl bonds</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9321,16 +8187,6 @@
           <t>thiol-dependent deubiquitinase ; deubiquitinase activity ; ubiquitin-like protein-specific protease activity</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9395,16 +8251,6 @@
           <t>transmembrane transport</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9472,16 +8318,6 @@
           <t>6-phosphofructokinase activity ; phosphofructokinase activity ; carbohydrate kinase activity</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9554,16 +8390,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9628,16 +8454,6 @@
           <t>metal ion binding ; nucleic acid binding</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9705,16 +8521,6 @@
           <t>annonymous</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9782,16 +8588,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9856,16 +8652,6 @@
           <t>acylphosphatase activity</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9938,16 +8724,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -10015,16 +8791,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -10092,16 +8858,6 @@
           <t>no function</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -10169,16 +8925,6 @@
           <t>positive regulation of transcription, DNA-templated</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -10246,16 +8992,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10328,16 +9064,6 @@
           <t>peptidyl-prolyl cis-trans isomerase activity</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -10410,16 +9136,6 @@
           <t>DNA binding ; ATP binding</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -10487,16 +9203,6 @@
           <t>transcription preinitiation complex assembly</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -10566,16 +9272,6 @@
           <t>DNA binding ; nucleic acid binding ; heterocyclic compound binding</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -10643,16 +9339,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -10720,16 +9406,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10797,16 +9473,6 @@
           <t>Protein of unknown function</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10874,16 +9540,6 @@
           <t>structural constituent of ribosome ; RNA binding</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10951,16 +9607,6 @@
           <t>regulation of proton transport ; regulation of cation transmembrane transport ; regulation of ion transmembrane transport</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11033,16 +9679,6 @@
           <t>transmembrane transporter activity ; transporter activity</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11110,16 +9746,6 @@
           <t>Protein of unknown function UPF0301 ; Thioredoxin-like superfamily</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11192,16 +9818,6 @@
           <t>integral component of membrane</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11271,16 +9887,6 @@
           <t>calcium ion binding</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11345,16 +9951,6 @@
           <t>sequence-specific DNA binding</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -11422,16 +10018,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -11501,16 +10087,6 @@
           <t>protein folding</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -11575,16 +10151,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -11654,16 +10220,6 @@
           <t>DNA binding</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -11736,16 +10292,6 @@
           <t>transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -11813,16 +10359,6 @@
           <t>ATP binding ; nucleic acid binding ; protein binding</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -11890,16 +10426,6 @@
           <t>protein serine/threonine phosphatase activity ; phosphoprotein phosphatase activity ; phosphatase activity</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -11964,16 +10490,6 @@
           <t>thiol-dependent deubiquitinase</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12041,16 +10557,6 @@
           <t>translation initiation factor activity ; translation factor activity, RNA binding ; translation regulator activity, nucleic acid binding</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -12115,16 +10621,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12197,16 +10693,6 @@
           <t>transferase activity</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12271,16 +10757,6 @@
           <t>No functional information found for HOM05D006296</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12345,16 +10821,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>#6641</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -12424,16 +10890,6 @@
           <t>GTPase activity ; GTP binding ; guanyl ribonucleotide binding</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12501,16 +10957,6 @@
           <t>ubiquitin conjugating enzyme activity</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12575,16 +11021,6 @@
           <t>clathrin binding</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12649,16 +11085,6 @@
           <t>process utilizing autophagic mechanism ; autophagy ; cellular catabolic process</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12726,16 +11152,6 @@
           <t>Protein of unknown function DUF616</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12803,16 +11219,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -12880,16 +11286,6 @@
           <t>Uncharacterized protein At1g76660-like</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12954,16 +11350,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -13031,16 +11417,6 @@
           <t>protein transport ; establishment of protein localization ; protein localization</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -13108,16 +11484,6 @@
           <t>Domain of unknown function DUF1308</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -13190,16 +11556,6 @@
           <t>myosin heavy chain binding ; myosin XI tail binding ; myosin tail binding</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -13269,16 +11625,6 @@
           <t>protein-disulfide reductase activity</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -13351,16 +11697,6 @@
           <t>peroxidase activity ; oxidoreductase activity, acting on peroxide as acceptor ; antioxidant activity</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13433,16 +11769,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13510,16 +11836,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13587,16 +11903,6 @@
           <t>ATP binding ; adenyl ribonucleotide binding ; adenyl nucleotide binding</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -13666,16 +11972,6 @@
           <t>alpha-amylase activity ; amylase activity ; calcium ion binding</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13743,16 +12039,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13820,16 +12106,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13894,16 +12170,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13973,16 +12239,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -14047,16 +12303,6 @@
           <t>Mitochondrial glycoprotein ; Mitochondrial glycoprotein superfamily</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -14121,16 +12367,6 @@
           <t>Trichome birefringence-like family ; PMR5 N-terminal domain ; PC-Esterase</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -14198,16 +12434,6 @@
           <t>protein heterodimerization activity ; protein dimerization activity ; protein binding</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -14275,16 +12501,6 @@
           <t>ATP hydrolysis activity ; ATP binding ; protein binding</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -14349,16 +12565,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -14423,16 +12629,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -14502,16 +12698,6 @@
           <t>dolichol kinase activity</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -14579,16 +12765,6 @@
           <t>No functional information found for ORTHO05D007246</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -14656,16 +12832,6 @@
           <t>Clp, repeat (R) domain ; Clp, N-terminal domain superfamily ; P-loop containing nucleoside triphosphate hydrolase</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -14730,16 +12896,6 @@
           <t>lipid metabolic process</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -14807,16 +12963,6 @@
           <t>acyltransferase activity, transferring groups other than amino-acyl groups ; acyltransferase activity ; transferase activity</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -14884,16 +13030,6 @@
           <t>Myb domain ; SANT/Myb domain ; Homeobox-like domain superfamily</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -14958,16 +13094,6 @@
           <t>structural constituent of ribosome ; structural molecule activity</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -15035,16 +13161,6 @@
           <t>ABC-type transporter activity ; ATPase-coupled transmembrane transporter activity ; primary active transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -15112,16 +13228,6 @@
           <t>ACT domain-containing protein ACR1-12</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -15187,16 +13293,6 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>protein binding</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -15211,7 +13307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R95"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15230,8 +13326,6 @@
     <col width="24" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="25" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15315,16 +13409,6 @@
           <t>gene function</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Angiosperm-353 loci ID</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>paralogs identification</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15397,16 +13481,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15474,16 +13548,6 @@
           <t>precatalytic spliceosome</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>#5858</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15553,16 +13617,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15635,16 +13689,6 @@
           <t>zinc ion binding</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15717,16 +13761,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15799,16 +13833,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -15876,16 +13900,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15953,16 +13967,6 @@
           <t>Peptidase C45</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16030,16 +14034,6 @@
           <t>isocitrate lyase activity ; oxo-acid-lyase activity ; carbon-carbon lyase activity</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16107,16 +14101,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -16184,16 +14168,6 @@
           <t>calcium-dependent phospholipid binding ; phospholipid binding ; lipid binding</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16261,16 +14235,6 @@
           <t>Protein of unknown function DUF1635</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16343,16 +14307,6 @@
           <t>ion channel activity ; channel activity ; passive transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16417,16 +14371,6 @@
           <t>unfolded protein binding ; ATP hydrolysis activity ; ATP binding</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16499,16 +14443,6 @@
           <t>Vacuolar protein sorting-associated protein 62</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16576,16 +14510,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16650,16 +14574,6 @@
           <t>hydrolase activity, hydrolyzing O-glycosyl compounds ; hydrolase activity, acting on glycosyl bonds</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16727,16 +14641,6 @@
           <t>thiol-dependent deubiquitinase ; deubiquitinase activity ; ubiquitin-like protein-specific protease activity</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16806,16 +14710,6 @@
           <t>transmembrane transport</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16883,16 +14777,6 @@
           <t>6-phosphofructokinase activity ; phosphofructokinase activity ; carbohydrate kinase activity</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16965,16 +14849,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -17039,16 +14913,6 @@
           <t>metal ion binding ; nucleic acid binding</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17116,16 +14980,6 @@
           <t>annonymous</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -17193,16 +15047,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -17267,16 +15111,6 @@
           <t>acylphosphatase activity</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17349,16 +15183,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17426,16 +15250,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17503,16 +15317,6 @@
           <t>no function</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17580,16 +15384,6 @@
           <t>positive regulation of transcription, DNA-templated</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17657,16 +15451,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17739,16 +15523,6 @@
           <t>peptidyl-prolyl cis-trans isomerase activity</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17821,16 +15595,6 @@
           <t>DNA binding ; ATP binding</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17903,16 +15667,6 @@
           <t>transcription preinitiation complex assembly</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17982,16 +15736,6 @@
           <t>DNA binding ; nucleic acid binding ; heterocyclic compound binding</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -18059,16 +15803,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18136,16 +15870,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18213,16 +15937,6 @@
           <t>Protein of unknown function</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18290,16 +16004,6 @@
           <t>structural constituent of ribosome ; RNA binding</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18367,16 +16071,6 @@
           <t>regulation of proton transport ; regulation of cation transmembrane transport ; regulation of ion transmembrane transport</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18449,16 +16143,6 @@
           <t>transmembrane transporter activity ; transporter activity</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18526,16 +16210,6 @@
           <t>Protein of unknown function UPF0301 ; Thioredoxin-like superfamily</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18608,16 +16282,6 @@
           <t>integral component of membrane</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18687,16 +16351,6 @@
           <t>calcium ion binding</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18761,16 +16415,6 @@
           <t>sequence-specific DNA binding</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18838,16 +16482,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -18917,16 +16551,6 @@
           <t>protein folding</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -18991,16 +16615,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -19070,16 +16684,6 @@
           <t>DNA binding</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -19152,16 +16756,6 @@
           <t>transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -19234,16 +16828,6 @@
           <t>ATP binding ; nucleic acid binding ; protein binding</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -19311,16 +16895,6 @@
           <t>protein serine/threonine phosphatase activity ; phosphoprotein phosphatase activity ; phosphatase activity</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -19385,16 +16959,6 @@
           <t>thiol-dependent deubiquitinase</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -19462,16 +17026,6 @@
           <t>translation initiation factor activity ; translation factor activity, RNA binding ; translation regulator activity, nucleic acid binding</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -19536,16 +17090,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19618,16 +17162,6 @@
           <t>transferase activity</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19692,16 +17226,6 @@
           <t>No functional information found for HOM05D006296</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19766,16 +17290,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>#6641</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19845,16 +17359,6 @@
           <t>GTPase activity ; GTP binding ; guanyl ribonucleotide binding</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19922,16 +17426,6 @@
           <t>ubiquitin conjugating enzyme activity</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19996,16 +17490,6 @@
           <t>clathrin binding</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -20070,16 +17554,6 @@
           <t>process utilizing autophagic mechanism ; autophagy ; cellular catabolic process</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -20147,16 +17621,6 @@
           <t>Protein of unknown function DUF616</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20224,16 +17688,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -20306,16 +17760,6 @@
           <t>Uncharacterized protein At1g76660-like</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20380,16 +17824,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -20462,16 +17896,6 @@
           <t>protein transport ; establishment of protein localization ; protein localization</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -20539,16 +17963,6 @@
           <t>Domain of unknown function DUF1308</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20621,16 +18035,6 @@
           <t>myosin heavy chain binding ; myosin XI tail binding ; myosin tail binding</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -20700,16 +18104,6 @@
           <t>protein-disulfide reductase activity</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20782,16 +18176,6 @@
           <t>peroxidase activity ; oxidoreductase activity, acting on peroxide as acceptor ; antioxidant activity</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20864,16 +18248,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -20941,16 +18315,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21018,16 +18382,6 @@
           <t>ATP binding ; adenyl ribonucleotide binding ; adenyl nucleotide binding</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21097,16 +18451,6 @@
           <t>alpha-amylase activity ; amylase activity ; calcium ion binding</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21179,16 +18523,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -21261,16 +18595,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -21335,16 +18659,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -21414,16 +18728,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="Q79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -21488,16 +18792,6 @@
           <t>Mitochondrial glycoprotein ; Mitochondrial glycoprotein superfamily</t>
         </is>
       </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -21562,16 +18856,6 @@
           <t>Trichome birefringence-like family ; PMR5 N-terminal domain ; PC-Esterase</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21644,16 +18928,6 @@
           <t>protein heterodimerization activity ; protein dimerization activity ; protein binding</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21721,16 +18995,6 @@
           <t>ATP hydrolysis activity ; ATP binding ; protein binding</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21800,16 +19064,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21874,16 +19128,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21953,16 +19197,6 @@
           <t>dolichol kinase activity</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -22035,16 +19269,6 @@
           <t>No functional information found for ORTHO05D007246</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22112,16 +19336,6 @@
           <t>Clp, repeat (R) domain ; Clp, N-terminal domain superfamily ; P-loop containing nucleoside triphosphate hydrolase</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22186,16 +19400,6 @@
           <t>lipid metabolic process</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22268,16 +19472,6 @@
           <t>acyltransferase activity, transferring groups other than amino-acyl groups ; acyltransferase activity ; transferase activity</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22350,16 +19544,6 @@
           <t>Myb domain ; SANT/Myb domain ; Homeobox-like domain superfamily</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -22424,16 +19608,6 @@
           <t>structural constituent of ribosome ; structural molecule activity</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -22501,16 +19675,6 @@
           <t>ABC-type transporter activity ; ATPase-coupled transmembrane transporter activity ; primary active transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -22578,16 +19742,6 @@
           <t>ACT domain-containing protein ACR1-12</t>
         </is>
       </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -22653,16 +19807,6 @@
       <c r="P95" t="inlineStr">
         <is>
           <t>protein binding</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -22677,7 +19821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y95"/>
+  <dimension ref="A1:V95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22702,8 +19846,6 @@
     <col width="24" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
     <col width="60" customWidth="1" min="22" max="22"/>
-    <col width="24" customWidth="1" min="23" max="23"/>
-    <col width="25" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22817,21 +19959,6 @@
           <t>gene function</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>Angiosperm-353 loci ID</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>paralogs identification</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22920,16 +20047,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23018,16 +20135,6 @@
           <t>precatalytic spliceosome</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>#5858</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23113,16 +20220,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23211,16 +20308,6 @@
           <t>zinc ion binding</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23309,16 +20396,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -23404,16 +20481,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23499,16 +20566,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23597,16 +20654,6 @@
           <t>Peptidase C45</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23695,16 +20742,6 @@
           <t>isocitrate lyase activity ; oxo-acid-lyase activity ; carbon-carbon lyase activity</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23793,16 +20830,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23891,16 +20918,6 @@
           <t>calcium-dependent phospholipid binding ; phospholipid binding ; lipid binding</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23989,16 +21006,6 @@
           <t>Protein of unknown function DUF1635</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -24087,16 +21094,6 @@
           <t>ion channel activity ; channel activity ; passive transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -24182,16 +21179,6 @@
           <t>unfolded protein binding ; ATP hydrolysis activity ; ATP binding</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24280,21 +21267,6 @@
           <t>Vacuolar protein sorting-associated protein 62</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Negative 2Δℓ: impossible for nested models, indicates a codeml optimisation failure; excluded from Figure 3B.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -24383,16 +21355,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -24478,16 +21440,6 @@
           <t>hydrolase activity, hydrolyzing O-glycosyl compounds ; hydrolase activity, acting on glycosyl bonds</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -24576,16 +21528,6 @@
           <t>thiol-dependent deubiquitinase ; deubiquitinase activity ; ubiquitin-like protein-specific protease activity</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -24671,16 +21613,6 @@
           <t>transmembrane transport</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -24769,16 +21701,6 @@
           <t>6-phosphofructokinase activity ; phosphofructokinase activity ; carbohydrate kinase activity</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -24867,16 +21789,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -24959,16 +21871,6 @@
           <t>metal ion binding ; nucleic acid binding</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -25039,16 +21941,6 @@
           <t>annonymous</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -25137,16 +22029,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -25229,16 +22111,6 @@
           <t>acylphosphatase activity</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -25327,16 +22199,6 @@
           <t>RNA binding</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -25425,16 +22287,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -25523,16 +22375,6 @@
           <t>no function</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -25621,16 +22463,6 @@
           <t>positive regulation of transcription, DNA-templated</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -25719,16 +22551,6 @@
           <t>protein binding ; binding</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -25817,16 +22639,6 @@
           <t>peptidyl-prolyl cis-trans isomerase activity</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -25915,16 +22727,6 @@
           <t>DNA binding ; ATP binding</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -26013,16 +22815,6 @@
           <t>transcription preinitiation complex assembly</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -26108,16 +22900,6 @@
           <t>DNA binding ; nucleic acid binding ; heterocyclic compound binding</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -26206,16 +22988,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -26301,16 +23073,6 @@
           <t>lipid binding</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -26393,16 +23155,6 @@
           <t>Protein of unknown function</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26491,16 +23243,6 @@
           <t>structural constituent of ribosome ; RNA binding</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26589,16 +23331,6 @@
           <t>regulation of proton transport ; regulation of cation transmembrane transport ; regulation of ion transmembrane transport</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26687,16 +23419,6 @@
           <t>transmembrane transporter activity ; transporter activity</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26785,16 +23507,6 @@
           <t>Protein of unknown function UPF0301 ; Thioredoxin-like superfamily</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26883,16 +23595,6 @@
           <t>integral component of membrane</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26978,16 +23680,6 @@
           <t>calcium ion binding</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -27073,16 +23765,6 @@
           <t>sequence-specific DNA binding</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -27171,16 +23853,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -27266,16 +23938,6 @@
           <t>protein folding</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -27361,16 +24023,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -27456,16 +24108,6 @@
           <t>DNA binding</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -27554,16 +24196,6 @@
           <t>transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -27646,16 +24278,6 @@
           <t>ATP binding ; nucleic acid binding ; protein binding</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -27744,16 +24366,6 @@
           <t>protein serine/threonine phosphatase activity ; phosphoprotein phosphatase activity ; phosphatase activity</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -27839,16 +24451,6 @@
           <t>thiol-dependent deubiquitinase</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -27937,16 +24539,6 @@
           <t>translation initiation factor activity ; translation factor activity, RNA binding ; translation regulator activity, nucleic acid binding</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -28026,16 +24618,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -28124,16 +24706,6 @@
           <t>transferase activity</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -28219,16 +24791,6 @@
           <t>No functional information found for HOM05D006296</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -28314,16 +24876,6 @@
           <t>protein kinase activity ; phosphotransferase activity, alcohol group as acceptor ; kinase activity</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>#6641</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -28409,16 +24961,6 @@
           <t>GTPase activity ; GTP binding ; guanyl ribonucleotide binding</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -28507,16 +25049,6 @@
           <t>ubiquitin conjugating enzyme activity</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -28602,16 +25134,6 @@
           <t>clathrin binding</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -28697,16 +25219,6 @@
           <t>process utilizing autophagic mechanism ; autophagy ; cellular catabolic process</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -28795,16 +25307,6 @@
           <t>Protein of unknown function DUF616</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28893,16 +25395,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -28991,16 +25483,6 @@
           <t>Uncharacterized protein At1g76660-like</t>
         </is>
       </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -29086,16 +25568,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X66" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -29184,16 +25656,6 @@
           <t>protein transport ; establishment of protein localization ; protein localization</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -29282,16 +25744,6 @@
           <t>Domain of unknown function DUF1308</t>
         </is>
       </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X68" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -29380,16 +25832,6 @@
           <t>myosin heavy chain binding ; myosin XI tail binding ; myosin tail binding</t>
         </is>
       </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -29475,16 +25917,6 @@
           <t>protein-disulfide reductase activity</t>
         </is>
       </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -29573,16 +26005,6 @@
           <t>peroxidase activity ; oxidoreductase activity, acting on peroxide as acceptor ; antioxidant activity</t>
         </is>
       </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X71" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -29671,16 +26093,6 @@
           <t>unknown function</t>
         </is>
       </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -29769,16 +26181,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -29867,16 +26269,6 @@
           <t>ATP binding ; adenyl ribonucleotide binding ; adenyl nucleotide binding</t>
         </is>
       </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -29962,16 +26354,6 @@
           <t>alpha-amylase activity ; amylase activity ; calcium ion binding</t>
         </is>
       </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -30060,16 +26442,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -30158,16 +26530,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -30253,16 +26615,6 @@
           <t>DNA-binding transcription factor activity ; transcription regulator activity ; DNA binding</t>
         </is>
       </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X78" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -30348,16 +26700,6 @@
           <t>protein serine/threonine kinase activity</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -30443,16 +26785,6 @@
           <t>Mitochondrial glycoprotein ; Mitochondrial glycoprotein superfamily</t>
         </is>
       </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X80" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -30538,16 +26870,6 @@
           <t>Trichome birefringence-like family ; PMR5 N-terminal domain ; PC-Esterase</t>
         </is>
       </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -30636,16 +26958,6 @@
           <t>protein heterodimerization activity ; protein dimerization activity ; protein binding</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -30728,16 +27040,6 @@
           <t>ATP hydrolysis activity ; ATP binding ; protein binding</t>
         </is>
       </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -30823,16 +27125,6 @@
           <t>protein binding</t>
         </is>
       </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -30918,16 +27210,6 @@
           <t>—</t>
         </is>
       </c>
-      <c r="W85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X85" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -31013,16 +27295,6 @@
           <t>dolichol kinase activity</t>
         </is>
       </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -31111,16 +27383,6 @@
           <t>No functional information found for ORTHO05D007246</t>
         </is>
       </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X87" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -31206,16 +27468,6 @@
           <t>Clp, repeat (R) domain ; Clp, N-terminal domain superfamily ; P-loop containing nucleoside triphosphate hydrolase</t>
         </is>
       </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -31298,16 +27550,6 @@
           <t>lipid metabolic process</t>
         </is>
       </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -31396,16 +27638,6 @@
           <t>acyltransferase activity, transferring groups other than amino-acyl groups ; acyltransferase activity ; transferase activity</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -31494,16 +27726,6 @@
           <t>Myb domain ; SANT/Myb domain ; Homeobox-like domain superfamily</t>
         </is>
       </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X91" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -31589,16 +27811,6 @@
           <t>structural constituent of ribosome ; structural molecule activity</t>
         </is>
       </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -31687,16 +27899,6 @@
           <t>ABC-type transporter activity ; ATPase-coupled transmembrane transporter activity ; primary active transmembrane transporter activity</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -31785,16 +27987,6 @@
           <t>ACT domain-containing protein ACR1-12</t>
         </is>
       </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X94" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -31881,16 +28073,6 @@
       <c r="V95" t="inlineStr">
         <is>
           <t>protein binding</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
